--- a/materialList.xlsx
+++ b/materialList.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremyschreier/Desktop/Virovory/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495CBDF3-6835-3344-8AA0-7514AF93E5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894E7DE0-ACC1-314A-B713-F1B9158FB3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10220" yWindow="500" windowWidth="23380" windowHeight="19720" xr2:uid="{07294BF3-7D2F-FC4B-A894-E8C433C58022}"/>
+    <workbookView xWindow="160" yWindow="600" windowWidth="19440" windowHeight="26520" activeTab="1" xr2:uid="{07294BF3-7D2F-FC4B-A894-E8C433C58022}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Updated" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="167">
   <si>
     <t>Cat #</t>
   </si>
@@ -289,12 +291,419 @@
   <si>
     <t>ThermoFisher</t>
   </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Ammonium Chloride</t>
+  </si>
+  <si>
+    <t>L-Proline</t>
+  </si>
+  <si>
+    <t>Walmart</t>
+  </si>
+  <si>
+    <t>Sigma</t>
+  </si>
+  <si>
+    <t>A9434-500G</t>
+  </si>
+  <si>
+    <t>https://www.sigmaaldrich.com/US/en/product/sigma/a9434</t>
+  </si>
+  <si>
+    <t>P5607-25G</t>
+  </si>
+  <si>
+    <t>25g</t>
+  </si>
+  <si>
+    <t>500g</t>
+  </si>
+  <si>
+    <t>https://www.sigmaaldrich.com/US/en/product/sigma/p5607</t>
+  </si>
+  <si>
+    <t>4 pack</t>
+  </si>
+  <si>
+    <t>https://www.walmart.com/ip/Coleman-All-Purpose-Propane-Gas-Cylinder-16-oz-4-Pack/47501438?classType=VARIANT&amp;athbdg=L1103&amp;from=/search</t>
+  </si>
+  <si>
+    <t>Coleman All Purpose Propane Gas Cylinder 16 oz</t>
+  </si>
+  <si>
+    <t>https://www.walmart.com/ip/DOMINOX-Propane-Torch-Head-Manual-Start-Solid-Brass-Brazing-Torch-Fuel-MAPP-MAP-Pro-Propane-CGA600-Cylinder-Bottle-Nozzle-Blow-Torch-Tip-Soldering-Br/5526112190?classType=REGULAR&amp;from=/search</t>
+  </si>
+  <si>
+    <t>DOMINOX propane torch head</t>
+  </si>
+  <si>
+    <t>Neoprene Bunsen Burner Hose, 3ft</t>
+  </si>
+  <si>
+    <t>23A00X843</t>
+  </si>
+  <si>
+    <t>Thomas Scientific</t>
+  </si>
+  <si>
+    <t>https://www.thomassci.com/p/neoprene-bunsen-burner-hose-3-ft-0-9m-long?q=23A00X843</t>
+  </si>
+  <si>
+    <t>1 pack</t>
+  </si>
+  <si>
+    <t>https://www.walmart.com/ip/24-Piece-Dinner-Spoons-Set-6-7-inch-Unokit-Stainless-Steel-Spoons-silverware-Dessert-Spoon-Tablespoon/17929311573?classType=REGULAR&amp;from=/search</t>
+  </si>
+  <si>
+    <t>24 piece Ruffulon Stainless steel spoons</t>
+  </si>
+  <si>
+    <t>Fisher</t>
+  </si>
+  <si>
+    <t>S02605</t>
+  </si>
+  <si>
+    <t>https://www.fishersci.com/shop/products/eisco-spatula-chattway-2/S02605#?keyword=spatula</t>
+  </si>
+  <si>
+    <t>20 cm Eisco Chattaway Lab Spatula</t>
+  </si>
+  <si>
+    <t>NaCl</t>
+  </si>
+  <si>
+    <t>Na2SO4</t>
+  </si>
+  <si>
+    <t>KCl</t>
+  </si>
+  <si>
+    <t>KBr</t>
+  </si>
+  <si>
+    <t>H3BO3</t>
+  </si>
+  <si>
+    <t>NaF</t>
+  </si>
+  <si>
+    <t>NaHCO3</t>
+  </si>
+  <si>
+    <t>MgCl2 6H2O</t>
+  </si>
+  <si>
+    <t>CaCl2 2H2O</t>
+  </si>
+  <si>
+    <t>SrCl2 6H2O</t>
+  </si>
+  <si>
+    <t>NaNO3</t>
+  </si>
+  <si>
+    <t>NaH2PO4 H2O</t>
+  </si>
+  <si>
+    <t>VWR</t>
+  </si>
+  <si>
+    <t>BDH9286-2.5KG</t>
+  </si>
+  <si>
+    <t>2.5 kg</t>
+  </si>
+  <si>
+    <t>https://www.avantorsciences.com/pr/en/product/NA2518509/sodium-chloride-990-acs-analytical-reagent-vwr-chemicals-bdh</t>
+  </si>
+  <si>
+    <r>
+      <t>Na</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>SO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <t>Kbr</t>
+  </si>
+  <si>
+    <r>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>BO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>NaHCO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MgCl2·6H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CaCl2·2H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SrCl2·6H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+  </si>
+  <si>
+    <t>50 L</t>
+  </si>
+  <si>
+    <t>100L</t>
+  </si>
+  <si>
+    <t>https://www.avantorsciences.com/us/en/product/4561204/sodium-sulfate-anhydrous-99-granules-ar-acs-acs-10---60-mesh-macron-fine-chemicals</t>
+  </si>
+  <si>
+    <t>MK8024-04</t>
+  </si>
+  <si>
+    <t>500 g</t>
+  </si>
+  <si>
+    <t>42348-500</t>
+  </si>
+  <si>
+    <t>MK5958-04</t>
+  </si>
+  <si>
+    <t>C7902-500G</t>
+  </si>
+  <si>
+    <t>100 g</t>
+  </si>
+  <si>
+    <t>100 kDa Amicon</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Bacterial growth</t>
+  </si>
+  <si>
+    <t>Bacterial Growth</t>
+  </si>
+  <si>
+    <t>Benchtop aseptic technique</t>
+  </si>
+  <si>
+    <t>Weighing chemicals</t>
+  </si>
+  <si>
+    <t>Making ASW</t>
+  </si>
+  <si>
+    <t>Making f/2 or L1</t>
+  </si>
+  <si>
+    <t>Washing/concentrating phage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAA1633922 </t>
+  </si>
+  <si>
+    <t>https://www.fishersci.com/shop/products/potassium-bromide-99-thermo-scientific/AAA1633922#potasium%20bromide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AA1159530 </t>
+  </si>
+  <si>
+    <t>250g</t>
+  </si>
+  <si>
+    <t>https://www.fishersci.com/shop/products/potassium-chloride-acs-99-0-100-5-thermo-scientific/AA1159530#?keyword=potasium%20chloride</t>
+  </si>
+  <si>
+    <t>https://www.fishersci.com/shop/products/boric-acid-99-6-acs-reagent-thermo-scientific/AC423485000#?keyword=42348-500</t>
+  </si>
+  <si>
+    <t>https://www.sigmaaldrich.com/US/en/product/sigald/201154</t>
+  </si>
+  <si>
+    <t>201154-100G</t>
+  </si>
+  <si>
+    <t>https://www.sigmaaldrich.com/US/en/product/sigma/s5761</t>
+  </si>
+  <si>
+    <t>https://www.avantorsciences.com/us/en/product/NA3427792/magnesium-chloride-hexahydrate-99-crystals-ar-acs-acs-macron-fine-chemicals?isCatNumSearch=true&amp;searchedCatalogNumber=MK5958-04</t>
+  </si>
+  <si>
+    <t>https://www.sigmaaldrich.com/US/en/product/sigma/c7902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AA3339322 </t>
+  </si>
+  <si>
+    <t>https://www.fishersci.com/shop/products/strontium-chloride-hexahydrate-acs-99-0-103-0-thermo-scientific/AA3339322#?keyword=33393</t>
+  </si>
+  <si>
+    <t>BDH4574-500G</t>
+  </si>
+  <si>
+    <t>https://www.avantorsciences.com/us/en/product/17598803/sodium-nitrate-990-crystallised-acs-vwr-chemicals-bdh</t>
+  </si>
+  <si>
+    <t>100g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01-337-702 </t>
+  </si>
+  <si>
+    <t>https://www.fishersci.com/shop/products/sodium-phosphate-monobasic-monohydrate-acs-reagent-sodium-dihydrogen-phosphate-reagents-3/01337702#?keyword=NaH2PO4%20H2O</t>
+  </si>
+  <si>
+    <t>24 pack</t>
+  </si>
+  <si>
+    <t>MillipreSigma</t>
+  </si>
+  <si>
+    <t>https://www.sigmaaldrich.com/US/en/product/mm/ufc9100</t>
+  </si>
+  <si>
+    <t>UFC910024</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -327,6 +736,33 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00000A"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color rgb="FF00000A"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -342,7 +778,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -368,11 +804,79 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -384,8 +888,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1198,4 +1719,614 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E69D1303-9AA8-9745-A7CD-E576749EFEDF}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" t="s">
+        <v>153</v>
+      </c>
+      <c r="F15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" t="s">
+        <v>154</v>
+      </c>
+      <c r="F16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F18" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>158</v>
+      </c>
+      <c r="B19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" t="s">
+        <v>165</v>
+      </c>
+      <c r="F21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{11997066-098D-864D-97AC-75EBA54DF1E6}"/>
+    <hyperlink ref="E7" r:id="rId2" xr:uid="{29C22B3C-2328-DD4A-9961-B08B2CFDAF1E}"/>
+    <hyperlink ref="E13" r:id="rId3" location="?keyword=42348-500" xr:uid="{E5773887-A1E3-9E40-8C96-432E1D302445}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB37C7C-51EC-E044-9B9C-3BC704C8224D}">
+  <dimension ref="A2:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="9">
+        <v>21.19</v>
+      </c>
+      <c r="C3">
+        <f>B3*50</f>
+        <v>1059.5</v>
+      </c>
+      <c r="D3">
+        <f>B3*100</f>
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="11">
+        <v>3.55</v>
+      </c>
+      <c r="C4">
+        <f>B4*50</f>
+        <v>177.5</v>
+      </c>
+      <c r="D4">
+        <f>B4*100</f>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="C5">
+        <f>B5*50</f>
+        <v>29.95</v>
+      </c>
+      <c r="D5">
+        <f>B5*100</f>
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="11">
+        <v>8.6199999999999999E-2</v>
+      </c>
+      <c r="C6">
+        <f>B6*50</f>
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="D6">
+        <f>B6*100</f>
+        <v>8.6199999999999992</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="11">
+        <v>2.29E-2</v>
+      </c>
+      <c r="C7">
+        <f>B7*50</f>
+        <v>1.145</v>
+      </c>
+      <c r="D7">
+        <f>B7*100</f>
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="11">
+        <v>2.7499999999999998E-3</v>
+      </c>
+      <c r="C8">
+        <f>B8*50</f>
+        <v>0.13749999999999998</v>
+      </c>
+      <c r="D8">
+        <f>B8*100</f>
+        <v>0.27499999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="11">
+        <v>0.17349999999999999</v>
+      </c>
+      <c r="C9">
+        <f>B9*50</f>
+        <v>8.6749999999999989</v>
+      </c>
+      <c r="D9">
+        <f>B9*100</f>
+        <v>17.349999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="37" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="9">
+        <v>9.5920000000000005</v>
+      </c>
+      <c r="C10">
+        <f>B10*50</f>
+        <v>479.6</v>
+      </c>
+      <c r="D10">
+        <f>B10*100</f>
+        <v>959.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="37" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="11">
+        <v>1.3440000000000001</v>
+      </c>
+      <c r="C11">
+        <f>B11*50</f>
+        <v>67.2</v>
+      </c>
+      <c r="D11">
+        <f>B11*100</f>
+        <v>134.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="37" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="11">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="C12">
+        <f>B12*50</f>
+        <v>1.095</v>
+      </c>
+      <c r="D12">
+        <f>B12*100</f>
+        <v>2.19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>